--- a/org_templates/organization_card_example.xlsx
+++ b/org_templates/organization_card_example.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
   <si>
     <t xml:space="preserve">№ п/п</t>
   </si>
@@ -213,7 +213,16 @@
     <t xml:space="preserve">Руководитель организации (должность, Ф.И.О. полностью)</t>
   </si>
   <si>
-    <t xml:space="preserve">Управляющий директор@Погосян А.А.</t>
+    <t xml:space="preserve">Должность</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ф.И.О.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Управляющий директор</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Погосян А.А.</t>
   </si>
   <si>
     <t xml:space="preserve">Председатель рабочей группы по проведению оценки профессиональных рисков (должность, Ф.И.О. полностью)</t>
@@ -222,7 +231,16 @@
     <t xml:space="preserve">Члены рабочей группы по проведению оценки профессиональных рисков (должность, Ф.И.О. полностью)</t>
   </si>
   <si>
-    <t xml:space="preserve">Главный инженер@Саевич И.И., Заместитель директора@Попов Т.А..</t>
+    <t xml:space="preserve">Заместитель управляющего директора</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Попов Т.А.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Главный инженер </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Саевич И.И.</t>
   </si>
 </sst>
 </file>
@@ -233,7 +251,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -261,6 +279,13 @@
       <name val="Arial Cyr"/>
       <family val="0"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -275,13 +300,6 @@
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
       <charset val="204"/>
     </font>
     <font>
@@ -305,6 +323,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -385,7 +410,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -398,27 +423,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -426,7 +455,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -434,19 +463,27 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -529,177 +566,241 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="42.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="61.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="76.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="40.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="4" width="40.84"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+    <row r="1" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="n">
+      <c r="D1" s="6"/>
+    </row>
+    <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="9" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="n">
+      <c r="D2" s="9"/>
+    </row>
+    <row r="3" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="n">
+      <c r="D3" s="9"/>
+    </row>
+    <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="10" t="n">
+      <c r="C4" s="11" t="n">
         <v>540501001</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="n">
+      <c r="D4" s="11"/>
+    </row>
+    <row r="5" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" s="11" t="n">
         <v>5407123450</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="n">
+      <c r="D5" s="11"/>
+    </row>
+    <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="11" t="n">
         <v>45189234</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="n">
+      <c r="D6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="11" t="n">
         <v>4210014</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="n">
+      <c r="D7" s="11"/>
+    </row>
+    <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="12" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="n">
+      <c r="D8" s="12"/>
+    </row>
+    <row r="9" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="11" t="n">
         <v>50701000001</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="56.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="n">
+      <c r="D9" s="11"/>
+    </row>
+    <row r="10" customFormat="false" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="13" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="56.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="n">
+      <c r="D10" s="13"/>
+    </row>
+    <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="14" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="56.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="n">
+      <c r="D11" s="15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="42.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B13" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="13" t="s">
+    </row>
+    <row r="14" customFormat="false" ht="42.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="14" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="56.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="14"/>
-    </row>
-    <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="15"/>
-    </row>
-    <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="14"/>
-    </row>
-    <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="19" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="29" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="32" customFormat="false" ht="8.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="33" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="D15" s="15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="42.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="42.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="17"/>
+      <c r="C17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="42.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="18"/>
+    </row>
+    <row r="19" customFormat="false" ht="42.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="17"/>
+    </row>
   </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/org_templates/organization_card_example.xlsx
+++ b/org_templates/organization_card_example.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
   <si>
     <t xml:space="preserve">№ п/п</t>
   </si>
@@ -210,13 +210,22 @@
     <t xml:space="preserve">630099, Новосибирская область, г. Новосибирск, ул. Молодежная, д. 12, пом. 3</t>
   </si>
   <si>
+    <t xml:space="preserve">Аудитор (должность, Ф.И.О. полностью)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Должность</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ф.И.О.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Эксперт по идентификации опасностей и оценке рисков</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Листикова Галина Михайловна</t>
+  </si>
+  <si>
     <t xml:space="preserve">Руководитель организации (должность, Ф.И.О. полностью)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Должность</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ф.И.О.</t>
   </si>
   <si>
     <t xml:space="preserve">Управляющий директор</t>
@@ -251,7 +260,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -329,22 +338,6 @@
       <sz val="12"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -410,16 +403,16 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -467,6 +460,10 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -475,15 +472,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -566,8 +563,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="42.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="61.29"/>
@@ -699,20 +696,20 @@
       <c r="A11" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="16" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="42.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="16" t="s">
+      <c r="B12" s="14"/>
+      <c r="C12" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="4" t="s">
@@ -726,21 +723,21 @@
       <c r="B13" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="16" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="42.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7"/>
       <c r="B14" s="8"/>
-      <c r="C14" s="16" t="s">
-        <v>19</v>
+      <c r="C14" s="18" t="s">
+        <v>22</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -748,42 +745,66 @@
         <v>12</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="16" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="42.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7"/>
       <c r="B16" s="8"/>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="42.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="17"/>
-      <c r="C17" s="3" t="s">
+    </row>
+    <row r="17" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="C17" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="42.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="18" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="42.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="18"/>
+      <c r="D18" s="4" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="42.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="17"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="42.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="19"/>
+    </row>
+    <row r="21" customFormat="false" ht="42.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="18">
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="C3:D3"/>
@@ -800,6 +821,8 @@
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="B15:B16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:B18"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/org_templates/organization_card_example.xlsx
+++ b/org_templates/organization_card_example.xlsx
@@ -10,6 +10,9 @@
   <sheets>
     <sheet name="Лист1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Лист1!$A$1:$D$19</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -460,7 +463,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -561,7 +564,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -826,7 +829,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="8" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
